--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC118"/>
+  <dimension ref="A1:AC119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q99" s="10" t="n">
         <v>2</v>
@@ -11421,11 +11421,11 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>6447</v>
+        <v>28680937</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Rainbow Toastmasters Club</t>
+          <t>Proconics Corporate</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -11443,13 +11443,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>0</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -11488,13 +11488,13 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="10" t="n">
-        <v>7</v>
+      <c r="X105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -11505,14 +11505,8 @@
       <c r="AA105" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB105" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB105" s="4" t="n"/>
+      <c r="AC105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11526,11 +11520,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28677015</v>
+        <v>6447</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Randwater Toastmasters</t>
+          <t>Rainbow Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -11548,13 +11542,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11593,13 +11587,13 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>0</v>
+      <c r="X106" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11611,9 +11605,13 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11623,19 +11621,19 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>920</v>
+        <v>28677015</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Florida Toastmasters Club</t>
+          <t>Randwater Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11649,13 +11647,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11679,7 +11677,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11694,25 +11692,25 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB107" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="W107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB107" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="AC107" s="4" t="inlineStr"/>
     </row>
@@ -11728,11 +11726,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28679195</v>
+        <v>920</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Industrial Development Corporation (IDC) Lion Pride</t>
+          <t>Florida Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11750,13 +11748,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11779,8 +11777,8 @@
       <c r="P108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" s="10" t="n">
-        <v>2</v>
+      <c r="Q108" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11795,7 +11793,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11806,20 +11804,16 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11833,11 +11827,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>934382</v>
+        <v>28679195</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Soweto Positive Speakers Club</t>
+          <t>Industrial Development Corporation (IDC) Lion Pride</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11855,10 +11849,10 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
         <v>0</v>
@@ -11882,16 +11876,16 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11911,18 +11905,18 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="10" t="n">
-        <v>1</v>
+      <c r="Z109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC109" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -11938,15 +11932,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>6413</v>
+        <v>934382</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>West Rand Toastmasters Club</t>
+          <t>Soweto Positive Speakers Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11960,10 +11954,10 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0</v>
@@ -11987,10 +11981,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q110" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -11998,8 +11992,8 @@
       <c r="S110" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
@@ -12016,8 +12010,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -12025,7 +12019,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12035,15 +12033,15 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>2025544</v>
+        <v>6413</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Bacon &amp; Egg</t>
+          <t>West Rand Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -12061,13 +12059,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12090,47 +12088,43 @@
       <c r="P111" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" s="9" t="n">
-        <v>1</v>
+      <c r="Q111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="10" t="n">
-        <v>4</v>
+      <c r="V111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="10" t="n">
-        <v>1</v>
+      <c r="Z111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC111" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12144,15 +12138,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>7534</v>
+        <v>2025544</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Golden Gavel Advanced Club</t>
+          <t>Bacon &amp; Egg</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12166,17 +12160,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -12193,10 +12187,10 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12204,14 +12198,14 @@
       <c r="S112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="10" t="n">
-        <v>1</v>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12222,16 +12216,20 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12245,15 +12243,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>9369</v>
+        <v>7534</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Honeydew Club</t>
+          <t>Golden Gavel Advanced Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12267,17 +12265,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12294,10 +12292,10 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q113" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12311,26 +12309,26 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="10" t="n">
+      <c r="V113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB113" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="W113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z113" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA113" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB113" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="AC113" s="4" t="inlineStr"/>
     </row>
@@ -12346,15 +12344,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>5585650</v>
+        <v>9369</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>The WesBank Toastmasters</t>
+          <t>Honeydew Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12368,10 +12366,10 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>4</v>
@@ -12395,10 +12393,10 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q114" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12406,8 +12404,8 @@
       <c r="S114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
+      <c r="T114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
@@ -12419,19 +12417,19 @@
         <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC114" s="4" t="inlineStr"/>
     </row>
@@ -12443,19 +12441,19 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>7535</v>
+        <v>5585650</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Carpe Diem Aspire</t>
+          <t>The WesBank Toastmasters</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12469,13 +12467,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12496,10 +12494,10 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12513,14 +12511,14 @@
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>0</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12532,7 +12530,7 @@
         <v>1</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AC115" s="4" t="inlineStr"/>
     </row>
@@ -12548,15 +12546,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>5579654</v>
+        <v>7535</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Moving Forward Toastmasters</t>
+          <t>Carpe Diem Aspire</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12570,13 +12568,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12597,37 +12595,37 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q116" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q116" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S116" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W116" s="10" t="n">
-        <v>7</v>
+      <c r="V116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="10" t="n">
-        <v>1</v>
+      <c r="Z116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12649,15 +12647,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>840322</v>
+        <v>5579654</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Rosebank Toastmasters Club</t>
+          <t>Moving Forward Toastmasters</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12671,13 +12669,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12698,13 +12696,13 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S117" s="10" t="n">
         <v>2</v>
@@ -12718,11 +12716,11 @@
       <c r="V117" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W117" s="9" t="n">
-        <v>3</v>
+      <c r="W117" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12734,13 +12732,9 @@
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC117" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -12754,15 +12748,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>8001302</v>
+        <v>840322</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Sasol Chemicals Ubuntu Toastmasters</t>
+          <t>Rosebank Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12776,13 +12770,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12811,44 +12805,149 @@
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+      <c r="S118" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>0</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="X118" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC118" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>8001302</v>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Sasol Chemicals Ubuntu Toastmasters</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J119" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O119" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB119" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC118" s="4" t="inlineStr">
+      <c r="AC119" s="4" t="inlineStr">
         <is>
           <t>Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC118"/>
+  <autoFilter ref="A1:AC119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13658,16 +13757,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -13676,7 +13775,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3407,7 +3411,11 @@
       <c r="AB26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4025,7 +4033,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4732,7 +4744,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -6990,7 +7006,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7398,7 +7418,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -7810,7 +7834,11 @@
       <c r="AB69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -9656,7 +9684,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9967,7 +9999,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10278,7 +10314,11 @@
       <c r="AB93" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -10892,7 +10932,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -11813,7 +11857,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -12124,7 +12172,11 @@
       <c r="AB111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12431,7 +12483,11 @@
       <c r="AB114" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC114" s="4" t="inlineStr"/>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12633,7 +12689,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12734,7 +12794,11 @@
       <c r="AB117" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC117" s="4" t="inlineStr"/>
+      <c r="AC117" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 61 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC119"/>
+  <dimension ref="A1:AC120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3612,8 +3612,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5668,8 +5668,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -6327,13 +6327,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6791,8 +6791,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6997,8 +6997,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7619,8 +7619,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7912,8 +7912,8 @@
       <c r="S70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
@@ -8722,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10893,8 +10893,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P99" s="9" t="n">
-        <v>3</v>
+      <c r="P99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q99" s="10" t="n">
         <v>2</v>
@@ -10902,8 +10902,8 @@
       <c r="R99" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S99" s="9" t="n">
-        <v>1</v>
+      <c r="S99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T99" s="10" t="n">
         <v>1</v>
@@ -11360,15 +11360,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28679069</v>
+        <v>28680375</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Mphatlalatsane Toastmasters</t>
+          <t>Linaleli Toastmasters</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11382,13 +11382,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11396,11 +11396,11 @@
         </is>
       </c>
       <c r="M104" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O104" s="7" t="inlineStr">
@@ -11409,31 +11409,31 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T104" s="10" t="n">
-        <v>1</v>
+      <c r="S104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="10" t="n">
-        <v>7</v>
+      <c r="X104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11441,17 +11441,11 @@
       <c r="Z104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA104" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB104" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC104" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AA104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="4" t="n"/>
+      <c r="AC104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11465,15 +11459,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28680937</v>
+        <v>28679069</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Proconics Corporate</t>
+          <t>Mphatlalatsane Toastmasters</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11487,13 +11481,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11514,31 +11508,31 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="S105" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="9" t="n">
-        <v>0</v>
+      <c r="X105" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -11549,8 +11543,14 @@
       <c r="AA105" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB105" s="4" t="n"/>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AB105" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11564,11 +11564,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>6447</v>
+        <v>28680937</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Rainbow Toastmasters Club</t>
+          <t>Proconics Corporate</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -11586,13 +11586,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>0</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11631,13 +11631,13 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="10" t="n">
-        <v>7</v>
+      <c r="X106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11648,14 +11648,8 @@
       <c r="AA106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB106" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC106" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB106" s="4" t="n"/>
+      <c r="AC106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11669,11 +11663,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28677015</v>
+        <v>6447</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Randwater Toastmasters</t>
+          <t>Rainbow Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11691,13 +11685,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11736,13 +11730,13 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="9" t="n">
-        <v>0</v>
+      <c r="X107" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11754,9 +11748,13 @@
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11766,19 +11764,19 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>920</v>
+        <v>28677015</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Florida Toastmasters Club</t>
+          <t>Randwater Toastmasters</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11792,13 +11790,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11822,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11837,31 +11835,27 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB108" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB108" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11875,11 +11869,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28679195</v>
+        <v>920</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Industrial Development Corporation (IDC) Lion Pride</t>
+          <t>Florida Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11897,13 +11891,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11926,8 +11920,8 @@
       <c r="P109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" s="10" t="n">
-        <v>2</v>
+      <c r="Q109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
@@ -11942,7 +11936,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11953,18 +11947,18 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC109" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -11980,11 +11974,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>934382</v>
+        <v>28679195</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Soweto Positive Speakers Club</t>
+          <t>Industrial Development Corporation (IDC) Lion Pride</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -12002,10 +11996,10 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0</v>
@@ -12029,16 +12023,16 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q110" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T110" s="9" t="n">
         <v>0</v>
@@ -12058,18 +12052,18 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -12085,15 +12079,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>6413</v>
+        <v>934382</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>West Rand Toastmasters Club</t>
+          <t>Soweto Positive Speakers Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12107,10 +12101,10 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
         <v>0</v>
@@ -12134,10 +12128,10 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q111" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="Q111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -12145,8 +12139,8 @@
       <c r="S111" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T111" s="10" t="n">
-        <v>1</v>
+      <c r="T111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
@@ -12163,8 +12157,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12174,7 +12168,7 @@
       </c>
       <c r="AC111" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -12186,15 +12180,15 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>2025544</v>
+        <v>6413</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Bacon &amp; Egg</t>
+          <t>West Rand Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -12212,13 +12206,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12241,45 +12235,45 @@
       <c r="P112" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q112" s="9" t="n">
-        <v>1</v>
+      <c r="Q112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="10" t="n">
-        <v>4</v>
+      <c r="V112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="10" t="n">
-        <v>1</v>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC112" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12295,15 +12289,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>7534</v>
+        <v>2025544</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Golden Gavel Advanced Club</t>
+          <t>Bacon &amp; Egg</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12317,17 +12311,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12344,10 +12338,10 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12355,14 +12349,14 @@
       <c r="S113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T113" s="10" t="n">
-        <v>1</v>
+      <c r="T113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12373,16 +12367,20 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12396,15 +12394,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>9369</v>
+        <v>7534</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Honeydew Club</t>
+          <t>Golden Gavel Advanced Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12418,17 +12416,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -12445,10 +12443,10 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q114" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12462,32 +12460,28 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="10" t="n">
+      <c r="V114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB114" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="W114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB114" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC114" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12501,15 +12495,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>5585650</v>
+        <v>9369</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>The WesBank Toastmasters</t>
+          <t>Honeydew Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12523,10 +12517,10 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>4</v>
@@ -12550,10 +12544,10 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12561,8 +12555,8 @@
       <c r="S115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="9" t="n">
-        <v>0</v>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U115" s="9" t="n">
         <v>0</v>
@@ -12574,21 +12568,25 @@
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -12598,19 +12596,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>7535</v>
+        <v>5585650</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Carpe Diem Aspire</t>
+          <t>The WesBank Toastmasters</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12624,13 +12622,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12651,10 +12649,10 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -12668,14 +12666,14 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>0</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -12687,13 +12685,9 @@
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC116" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12707,15 +12701,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>5579654</v>
+        <v>7535</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Moving Forward Toastmasters</t>
+          <t>Carpe Diem Aspire</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12729,13 +12723,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12756,37 +12750,37 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q117" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q117" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S117" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T117" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W117" s="10" t="n">
-        <v>8</v>
+      <c r="V117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12812,15 +12806,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>840322</v>
+        <v>5579654</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Rosebank Toastmasters Club</t>
+          <t>Moving Forward Toastmasters</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12834,13 +12828,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12861,13 +12855,13 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q118" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R118" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S118" s="10" t="n">
         <v>2</v>
@@ -12881,11 +12875,11 @@
       <c r="V118" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W118" s="9" t="n">
-        <v>3</v>
+      <c r="W118" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12897,11 +12891,11 @@
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12917,15 +12911,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>8001302</v>
+        <v>840322</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Sasol Chemicals Ubuntu Toastmasters</t>
+          <t>Rosebank Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12939,13 +12933,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12974,44 +12968,149 @@
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
+      <c r="S119" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>0</v>
+      <c r="V119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="X119" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>8001302</v>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Sasol Chemicals Ubuntu Toastmasters</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J120" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M120" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O120" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB120" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC119" s="4" t="inlineStr">
+      <c r="AC120" s="4" t="inlineStr">
         <is>
           <t>Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC119"/>
+  <autoFilter ref="A1:AC120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13296,7 +13395,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13461,7 +13560,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13527,7 +13626,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13560,7 +13659,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13593,7 +13692,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13791,13 +13890,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -13821,25 +13920,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -13923,7 +14022,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 61 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="P3" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R3" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" s="10" t="n">
         <v>3</v>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1338,8 +1338,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2140,8 +2140,8 @@
       <c r="S14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="9" t="n">
-        <v>0</v>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
@@ -2158,8 +2158,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2347,11 +2347,11 @@
       <c r="R16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="9" t="n">
-        <v>0</v>
+      <c r="S16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
@@ -2368,8 +2368,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3301,8 +3301,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3818,8 +3818,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3892,8 +3892,8 @@
       <c r="P31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="9" t="n">
-        <v>1</v>
+      <c r="Q31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>0</v>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4331,8 +4331,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4533,8 +4533,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="10" t="n">
         <v>1</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5028,8 +5028,8 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
@@ -5046,8 +5046,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5647,8 +5647,8 @@
       <c r="R48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="9" t="n">
-        <v>0</v>
+      <c r="S48" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T48" s="9" t="n">
         <v>0</v>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5971,8 +5971,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6282,8 +6282,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6365,8 +6365,8 @@
       <c r="S55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T55" s="9" t="n">
-        <v>0</v>
+      <c r="T55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U55" s="9" t="n">
         <v>0</v>
@@ -6458,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J62" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>11</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>1</v>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7304,8 +7304,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7769,13 +7769,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8641,8 +8641,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8742,8 +8742,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -9102,13 +9102,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9652,7 +9652,7 @@
         <v>2</v>
       </c>
       <c r="R87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" s="9" t="n">
         <v>0</v>
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9990,8 +9990,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10445,7 +10445,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10515,8 +10515,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10647,7 +10647,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10717,8 +10717,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10903,7 +10903,7 @@
         <v>2</v>
       </c>
       <c r="S99" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T99" s="10" t="n">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11537,8 +11537,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -11927,7 +11927,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12052,8 +12052,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -12087,7 +12087,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12127,8 +12127,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P111" s="9" t="n">
-        <v>3</v>
+      <c r="P111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12262,8 +12262,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12779,8 +12779,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13197,7 +13197,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -13230,7 +13230,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13296,7 +13296,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13362,7 +13362,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13395,7 +13395,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13428,7 +13428,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13494,7 +13494,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13659,7 +13659,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13758,7 +13758,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13824,7 +13824,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -13857,7 +13857,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -13923,7 +13923,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13956,7 +13956,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14022,7 +14022,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 37 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC120"/>
+  <dimension ref="A1:AC123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="P3" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>2</v>
@@ -1015,7 +1015,7 @@
         <v>4</v>
       </c>
       <c r="W3" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>7</v>
@@ -1072,17 +1072,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="P5" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="9" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1383,17 +1383,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1427,8 +1427,8 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>0</v>
+      <c r="V7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1629,8 +1629,8 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>2</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1686,17 +1686,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="9" t="n">
         <v>0</v>
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1896,17 +1896,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-36</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -2001,17 +2001,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -2102,17 +2102,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2312,17 +2312,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2619,17 +2619,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="8" t="n">
@@ -2724,17 +2724,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-29</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2974,11 +2974,11 @@
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="9" t="n">
-        <v>0</v>
+      <c r="V22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>7</v>
@@ -2986,8 +2986,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
+        <v>-15</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3289,8 +3289,8 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>1</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3346,13 +3346,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3393,8 +3393,8 @@
       <c r="V26" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>0</v>
+      <c r="W26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>7</v>
@@ -3451,17 +3451,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3863,17 +3863,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3968,17 +3968,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4477,17 +4477,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4578,13 +4578,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4679,13 +4679,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4717,8 +4717,8 @@
       <c r="S39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="9" t="n">
-        <v>0</v>
+      <c r="T39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>0</v>
@@ -4727,7 +4727,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>5</v>
@@ -4784,13 +4784,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4885,13 +4885,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4990,17 +4990,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5196,17 +5196,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>1</v>
@@ -5346,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5406,13 +5406,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>7</v>
@@ -5511,13 +5511,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5612,13 +5612,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
@@ -5915,17 +5915,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6226,17 +6226,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>10</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6270,11 +6270,11 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="9" t="n">
-        <v>0</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W54" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X54" s="9" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6428,13 +6428,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6529,17 +6529,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6573,11 +6573,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
+      <c r="V57" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W57" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W57" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>6</v>
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6735,17 +6735,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6780,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6941,17 +6941,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -7046,13 +7046,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7222,15 +7222,15 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>3330</v>
+        <v>28681009</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Crest Connect Club</t>
+          <t>uMgeni-uThukela North Zone Toastmasters Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -7248,17 +7248,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7293,13 +7293,13 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X64" s="10" t="n">
-        <v>7</v>
+      <c r="X64" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
@@ -7310,14 +7310,8 @@
       <c r="AA64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB64" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC64" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB64" s="4" t="n"/>
+      <c r="AC64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7331,11 +7325,11 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>5906</v>
+        <v>3330</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Highway Club</t>
+          <t>Crest Connect Club</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -7353,17 +7347,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7380,7 +7374,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7398,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7416,11 +7410,11 @@
         <v>1</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC65" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -7436,11 +7430,11 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>5059528</v>
+        <v>5906</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Kloof Toastmasters Business Club</t>
+          <t>Highway Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -7461,10 +7455,10 @@
         <v>19</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>-22</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7485,7 +7479,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7494,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66" s="9" t="n">
         <v>0</v>
@@ -7503,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7521,11 +7515,11 @@
         <v>1</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -7541,11 +7535,11 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>28678628</v>
+        <v>5059528</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Toast and Talk Toastmasters Club</t>
+          <t>Kloof Toastmasters Business Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -7563,13 +7557,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7590,7 +7584,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7608,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7626,9 +7620,13 @@
         <v>1</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC67" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC67" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7638,15 +7636,15 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1590</v>
+        <v>28678628</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Pietermaritzburg Toastmasters Club</t>
+          <t>Toast and Talk Toastmasters Club</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -7664,13 +7662,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7699,8 +7697,8 @@
       <c r="R68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="10" t="n">
-        <v>2</v>
+      <c r="S68" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T68" s="9" t="n">
         <v>0</v>
@@ -7708,14 +7706,14 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>1</v>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X68" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -7727,13 +7725,9 @@
         <v>1</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC68" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="AC68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -7747,15 +7741,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>6955849</v>
+        <v>7205986</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Pinnacle Toastmasters Club</t>
+          <t>Lunch &amp; Learn Toastmasters Club</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7769,17 +7763,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7795,50 +7789,46 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P69" s="10" t="n">
+      <c r="P69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V69" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" s="10" t="n">
+      <c r="Y69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB69" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB69" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC69" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7852,15 +7842,15 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>7205986</v>
+        <v>1590</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>The MultiVoice Academy</t>
+          <t>Pietermaritzburg Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7874,13 +7864,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7901,7 +7891,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -7909,29 +7899,29 @@
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="10" t="n">
-        <v>1</v>
+      <c r="S70" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T70" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7939,7 +7929,11 @@
       <c r="AB70" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7953,15 +7947,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>28679921</v>
+        <v>6955849</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Time to Talk Toastmasters</t>
+          <t>Pinnacle Toastmasters Club</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7975,13 +7969,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8001,32 +7995,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P71" s="9" t="n">
+      <c r="P71" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q71" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q71" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" s="9" t="n">
-        <v>0</v>
+      <c r="T71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -8038,9 +8032,13 @@
         <v>1</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8050,15 +8048,15 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>7205939</v>
+        <v>28679921</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Multichoice Toasties</t>
+          <t>Time to Talk Toastmasters</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -8076,25 +8074,25 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O72" s="7" t="inlineStr">
@@ -8106,22 +8104,22 @@
         <v>2</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T72" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T72" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8135,11 +8133,11 @@
       <c r="Z72" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA72" s="9" t="n">
-        <v>0</v>
+      <c r="AA72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC72" s="4" t="inlineStr"/>
     </row>
@@ -8151,19 +8149,19 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>6955072</v>
+        <v>28681012</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Nedbank Next Gen Toastmasters</t>
+          <t>uMgeni-uThukela Central Toastmasters Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8177,25 +8175,25 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
@@ -8233,15 +8231,13 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
@@ -8256,11 +8252,11 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>7894828</v>
+        <v>7205939</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Sell the Sizzle</t>
+          <t>Multichoice Toasties</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -8278,10 +8274,10 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K74" s="4" t="n">
         <v>2</v>
@@ -8292,11 +8288,11 @@
         </is>
       </c>
       <c r="M74" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
@@ -8305,16 +8301,16 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="10" t="n">
         <v>1</v>
@@ -8329,16 +8325,16 @@
         <v>0</v>
       </c>
       <c r="X74" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="10" t="n">
-        <v>1</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB74" s="4" t="n">
         <v>2</v>
@@ -8357,11 +8353,11 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>2566709</v>
+        <v>6955072</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>The Keynote Club: IQbusiness Toastmasters</t>
+          <t>Nedbank Next Gen Toastmasters</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -8379,13 +8375,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8424,13 +8420,13 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X75" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8442,7 +8438,7 @@
         <v>0</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC75" s="4" t="inlineStr"/>
     </row>
@@ -8458,15 +8454,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>5820462</v>
+        <v>7894828</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>The Professionals Club</t>
+          <t>Sell the Sizzle</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8480,13 +8476,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8507,7 +8503,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>0</v>
@@ -8518,20 +8514,20 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8543,136 +8539,132 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC76" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>3008</v>
+        <v>2566709</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>4th Dimension Club</t>
+          <t>The Keynote Club: IQbusiness Toastmasters</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F77" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J77" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K77" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M77" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O77" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P77" s="9" t="n">
+      <c r="Y77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="Q77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X77" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB77" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="AC77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1496354</v>
+        <v>5820462</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>5th Dimension Toastmasters Club</t>
+          <t>The Professionals Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8686,17 +8678,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8713,37 +8705,37 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="10" t="n">
-        <v>1</v>
+      <c r="Z78" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8760,24 +8752,24 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>4750197</v>
+        <v>28681007</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Bryanston Breakfast Toastmasters Club</t>
+          <t>uMgeni-uThukela South Central Toastmasters Club</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8791,17 +8783,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L79" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8836,26 +8828,24 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB79" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB79" s="4" t="n"/>
       <c r="AC79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
@@ -8870,15 +8860,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1798</v>
+        <v>3008</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Egoli Golden City Club</t>
+          <t>4th Dimension Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8892,13 +8882,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8919,28 +8909,28 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T80" s="9" t="n">
-        <v>0</v>
+      <c r="S80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W80" s="9" t="n">
-        <v>0</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W80" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>7</v>
@@ -8955,13 +8945,9 @@
         <v>1</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC80" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -8975,15 +8961,15 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>2934</v>
+        <v>1496354</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Randburg Toastmasters</t>
+          <t>5th Dimension Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8997,17 +8983,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -9033,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
@@ -9041,14 +9027,14 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="10" t="n">
-        <v>4</v>
+      <c r="V81" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9060,11 +9046,11 @@
         <v>1</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC81" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -9076,19 +9062,19 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>28678340</v>
+        <v>4750197</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>MunSoft Toastmasters Club</t>
+          <t>Bryanston Breakfast Toastmasters Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9102,13 +9088,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9146,14 +9132,14 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>2</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -9177,19 +9163,19 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>28678341</v>
+        <v>1798</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>MunSoft2 Toastmasters Club</t>
+          <t>Egoli Golden City Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9203,13 +9189,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9233,13 +9219,13 @@
         <v>0</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S83" s="9" t="n">
-        <v>0</v>
+      <c r="S83" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T83" s="9" t="n">
         <v>0</v>
@@ -9248,27 +9234,31 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>1</v>
+      <c r="X83" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9278,19 +9268,19 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>2902</v>
+        <v>2934</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Nedbank Club</t>
+          <t>Randburg Toastmasters</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9304,17 +9294,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9331,7 +9321,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9342,36 +9332,36 @@
       <c r="S84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="10" t="n">
-        <v>1</v>
+      <c r="T84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>0</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -9387,15 +9377,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>28675454</v>
+        <v>28678340</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Nedbank Executive Toastmasters Club</t>
+          <t>MunSoft Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9409,17 +9399,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9439,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
@@ -9459,26 +9449,22 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="10" t="n">
-        <v>6</v>
+      <c r="X85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="10" t="n">
-        <v>1</v>
+      <c r="Z85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC85" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9492,15 +9478,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>862</v>
+        <v>28678341</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>SpeechQuest</t>
+          <t>MunSoft2 Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9514,13 +9500,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9552,38 +9538,34 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U86" s="10" t="n">
+      <c r="T86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB86" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB86" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC86" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9593,19 +9575,19 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>8217</v>
+        <v>2902</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Morningside Toastmasters</t>
+          <t>Nedbank Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9619,17 +9601,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9646,13 +9628,13 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q87" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
         <v>0</v>
@@ -9664,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9675,18 +9657,18 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="10" t="n">
-        <v>1</v>
+      <c r="Z87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC87" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -9698,19 +9680,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>7934401</v>
+        <v>28675454</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Nedbank Allstars</t>
+          <t>Nedbank Executive Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9724,17 +9706,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9753,29 +9735,29 @@
       <c r="P88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" s="10" t="n">
+      <c r="Q88" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T88" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X88" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9787,7 +9769,7 @@
         <v>1</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC88" s="4" t="inlineStr">
         <is>
@@ -9803,19 +9785,19 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>5624</v>
+        <v>862</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Rivonia Toastmasters Club</t>
+          <t>SpeechQuest</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9829,17 +9811,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9858,29 +9840,29 @@
       <c r="P89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" s="10" t="n">
+      <c r="Q89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" s="10" t="n">
-        <v>4</v>
+      <c r="V89" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9892,11 +9874,11 @@
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC89" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -9912,15 +9894,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>4718</v>
+        <v>8217</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Sandton Toastmasters Club</t>
+          <t>Morningside Toastmasters</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9934,13 +9916,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9961,31 +9943,31 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T90" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
+      <c r="V90" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W90" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W90" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X90" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -10017,15 +9999,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4500</v>
+        <v>7934401</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Transformers Toastmasters Club</t>
+          <t>Nedbank Allstars</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10039,13 +10021,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10068,29 +10050,29 @@
       <c r="P91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" s="9" t="n">
-        <v>1</v>
+      <c r="Q91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="T91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10102,11 +10084,11 @@
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC91" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -10118,19 +10100,19 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>7638051</v>
+        <v>5624</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Harties Toastmasters Club</t>
+          <t>Rivonia Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10144,13 +10126,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10173,8 +10155,8 @@
       <c r="P92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" s="9" t="n">
-        <v>0</v>
+      <c r="Q92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -10182,17 +10164,17 @@
       <c r="S92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>7</v>
@@ -10200,18 +10182,18 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -10223,15 +10205,15 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>6489143</v>
+        <v>4718</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>SAP Toastmasters</t>
+          <t>Sandton Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -10249,17 +10231,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10285,7 +10267,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -10294,13 +10276,13 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10328,19 +10310,19 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>7865099</v>
+        <v>4500</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Thriving Toastmasters</t>
+          <t>Transformers Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10354,13 +10336,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10368,11 +10350,11 @@
         </is>
       </c>
       <c r="M94" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O94" s="7" t="inlineStr">
@@ -10390,7 +10372,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T94" s="9" t="n">
         <v>0</v>
@@ -10398,26 +10380,26 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>1</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X94" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="X94" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
@@ -10437,15 +10419,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>28679391</v>
+        <v>7638051</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Toyota South Africa</t>
+          <t>Harties Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10459,17 +10441,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10486,7 +10468,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10510,21 +10492,25 @@
         <v>0</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="10" t="n">
-        <v>1</v>
+      <c r="Z95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB95" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10538,15 +10524,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>6570123</v>
+        <v>6489143</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Woodlands Office Park</t>
+          <t>SAP Toastmasters</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10560,13 +10546,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>-22</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10605,27 +10591,31 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X96" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10635,19 +10625,19 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>934378</v>
+        <v>7865099</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Eloquent Speakers Club</t>
+          <t>Thriving Toastmasters</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10661,72 +10651,76 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M97" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O97" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L97" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M97" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N97" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O97" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P97" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q97" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA97" s="10" t="n">
-        <v>1</v>
+      <c r="Z97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC97" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10736,19 +10730,19 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>7031701</v>
+        <v>28679391</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Gaborone Breakfast</t>
+          <t>Toyota South Africa</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10762,17 +10756,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L98" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10789,7 +10783,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>0</v>
@@ -10809,8 +10803,8 @@
       <c r="V98" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W98" s="9" t="n">
-        <v>0</v>
+      <c r="W98" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>6</v>
@@ -10818,20 +10812,16 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC98" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -10841,19 +10831,19 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>8699</v>
+        <v>6570123</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Gaborone Toastmasters</t>
+          <t>Woodlands Office Park</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10867,17 +10857,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10893,50 +10883,46 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P99" s="10" t="n">
+      <c r="P99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q99" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R99" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S99" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T99" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="10" t="n">
-        <v>1</v>
+      <c r="Z99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB99" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC99" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10950,15 +10936,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>28680930</v>
+        <v>934378</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Mutual Impact Toastmasters Club</t>
+          <t>Eloquent Speakers Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10972,17 +10958,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10999,42 +10985,44 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q100" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
+      <c r="S100" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>0</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X100" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB100" s="4" t="n"/>
+      <c r="AB100" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="AC100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
@@ -11049,11 +11037,11 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28678784</v>
+        <v>7031701</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>New Age Orators</t>
+          <t>Gaborone Breakfast</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -11071,17 +11059,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11115,8 +11103,8 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>3</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11127,8 +11115,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="10" t="n">
-        <v>1</v>
+      <c r="Z101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11154,15 +11142,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>7452611</v>
+        <v>8699</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>SpeakEasy Botswana</t>
+          <t>Gaborone Toastmasters</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11176,13 +11164,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>7</v>
+        <v>-19</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11202,17 +11190,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="9" t="n">
-        <v>0</v>
+      <c r="P102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R102" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S102" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T102" s="10" t="n">
         <v>1</v>
@@ -11224,10 +11212,10 @@
         <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11239,31 +11227,35 @@
         <v>1</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>4775984</v>
+        <v>28680930</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Bloemfontein Toastmasters Club</t>
+          <t>Mutual Impact Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11277,13 +11269,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11322,53 +11314,47 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="10" t="n">
-        <v>7</v>
+      <c r="X103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="10" t="n">
-        <v>1</v>
+      <c r="Z103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB103" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC103" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AB103" s="4" t="n"/>
+      <c r="AC103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28680375</v>
+        <v>28678784</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Linaleli Toastmasters</t>
+          <t>New Age Orators</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11382,10 +11368,10 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K104" s="4" t="n">
         <v>0</v>
@@ -11396,11 +11382,11 @@
         </is>
       </c>
       <c r="M104" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O104" s="7" t="inlineStr">
@@ -11427,47 +11413,53 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>0</v>
+      <c r="X104" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" s="4" t="n"/>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA104" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB104" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28679069</v>
+        <v>7452611</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Mphatlalatsane Toastmasters</t>
+          <t>SpeakEasy Botswana</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11481,13 +11473,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11508,10 +11500,10 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -11525,14 +11517,14 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W105" s="9" t="n">
-        <v>0</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X105" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -11544,13 +11536,9 @@
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11564,15 +11552,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>28680937</v>
+        <v>4775984</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Proconics Corporate</t>
+          <t>Bloemfontein Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11586,17 +11574,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11631,25 +11619,31 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>0</v>
+      <c r="X106" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB106" s="4" t="n"/>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AB106" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11663,11 +11657,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>6447</v>
+        <v>28680375</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Rainbow Toastmasters Club</t>
+          <t>Linaleli Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11685,13 +11679,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11699,11 +11693,11 @@
         </is>
       </c>
       <c r="M107" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O107" s="7" t="inlineStr">
@@ -11715,7 +11709,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11730,31 +11724,25 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="10" t="n">
-        <v>7</v>
+      <c r="X107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB107" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="4" t="n"/>
+      <c r="AC107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11768,15 +11756,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28677015</v>
+        <v>28679069</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Randwater Toastmasters</t>
+          <t>Mphatlalatsane Toastmasters</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11790,17 +11778,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11817,7 +11805,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>1</v>
@@ -11825,37 +11813,41 @@
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
+      <c r="S108" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>0</v>
+      <c r="X108" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11865,15 +11857,15 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>920</v>
+        <v>28680937</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Florida Toastmasters Club</t>
+          <t>Proconics Corporate</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11891,13 +11883,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11927,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11936,13 +11928,13 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="10" t="n">
-        <v>7</v>
+      <c r="X109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11953,14 +11945,8 @@
       <c r="AA109" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB109" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC109" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB109" s="4" t="n"/>
+      <c r="AC109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -11970,15 +11956,15 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28679195</v>
+        <v>6447</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Industrial Development Corporation (IDC) Lion Pride</t>
+          <t>Rainbow Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11996,13 +11982,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12023,10 +12009,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q110" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12040,11 +12026,11 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" s="9" t="n">
-        <v>0</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W110" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -12052,8 +12038,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="10" t="n">
-        <v>1</v>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -12075,19 +12061,19 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>934382</v>
+        <v>28677015</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Soweto Positive Speakers Club</t>
+          <t>Randwater Toastmasters</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12101,17 +12087,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12127,17 +12113,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P111" s="10" t="n">
-        <v>4</v>
+      <c r="P111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S111" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T111" s="9" t="n">
         <v>0</v>
@@ -12151,26 +12137,22 @@
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="10" t="n">
-        <v>7</v>
+      <c r="X111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="10" t="n">
-        <v>1</v>
+      <c r="Z111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC111" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12184,15 +12166,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>6413</v>
+        <v>920</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>West Rand Toastmasters Club</t>
+          <t>Florida Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12206,13 +12188,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12233,10 +12215,10 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q112" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12244,14 +12226,14 @@
       <c r="S112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T112" s="10" t="n">
-        <v>1</v>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12285,19 +12267,19 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2025544</v>
+        <v>28679195</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Bacon &amp; Egg</t>
+          <t>Industrial Development Corporation (IDC) Lion Pride</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12311,17 +12293,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J113" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="J113" s="4" t="n">
-        <v>21</v>
-      </c>
       <c r="K113" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12338,10 +12320,10 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q113" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12359,10 +12341,10 @@
         <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12374,11 +12356,11 @@
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC113" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -12390,19 +12372,19 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>7534</v>
+        <v>934382</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Golden Gavel Advanced Club</t>
+          <t>Soweto Positive Speakers Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12416,13 +12398,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12442,8 +12424,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P114" s="9" t="n">
-        <v>0</v>
+      <c r="P114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12452,36 +12434,40 @@
         <v>0</v>
       </c>
       <c r="S114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC114" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12491,19 +12477,19 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>9369</v>
+        <v>6413</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Honeydew Club</t>
+          <t>West Rand Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12517,17 +12503,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12544,7 +12530,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q115" s="10" t="n">
         <v>2</v>
@@ -12553,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" s="10" t="n">
         <v>1</v>
@@ -12561,8 +12547,8 @@
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="10" t="n">
-        <v>4</v>
+      <c r="V115" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12600,15 +12586,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>5585650</v>
+        <v>2025544</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>The WesBank Toastmasters</t>
+          <t>Bacon &amp; Egg</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12622,17 +12608,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12649,10 +12635,10 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -12670,24 +12656,28 @@
         <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12697,15 +12687,15 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>7535</v>
+        <v>7534</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Carpe Diem Aspire</t>
+          <t>Golden Gavel Advanced Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -12723,17 +12713,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12750,10 +12740,10 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12761,8 +12751,8 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
@@ -12774,25 +12764,21 @@
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC117" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -12802,19 +12788,19 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>5579654</v>
+        <v>9369</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Moving Forward Toastmasters</t>
+          <t>Honeydew Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12828,13 +12814,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>12</v>
+        <v>-8</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12855,16 +12841,16 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q118" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R118" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S118" s="10" t="n">
-        <v>2</v>
+      <c r="R118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
@@ -12875,8 +12861,8 @@
       <c r="V118" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W118" s="10" t="n">
-        <v>8</v>
+      <c r="W118" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>7</v>
@@ -12907,43 +12893,43 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>840322</v>
+        <v>5585650</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Rosebank Toastmasters Club</t>
+          <t>The WesBank Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F119" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G119" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="J119" s="4" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-31</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12968,11 +12954,11 @@
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S119" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T119" s="10" t="n">
-        <v>1</v>
+      <c r="S119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
@@ -12981,28 +12967,24 @@
         <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB119" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="X119" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z119" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA119" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB119" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC119" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -13016,15 +12998,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>8001302</v>
+        <v>7535</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Sasol Chemicals Ubuntu Toastmasters</t>
+          <t>Carpe Diem Aspire</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13038,13 +13020,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13065,10 +13047,10 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -13083,34 +13065,349 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="9" t="n">
+      <c r="X120" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB120" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>5579654</v>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Moving Forward Toastmasters</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J121" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K121" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M121" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O121" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P121" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R121" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Y120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB120" s="4" t="n">
+      <c r="S121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W121" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X121" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC121" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>840322</v>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Rosebank Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J122" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K122" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M122" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X122" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB122" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>8001302</v>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Sasol Chemicals Ubuntu Toastmasters</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K123" s="4" t="n">
+        <v>-23</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M123" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O123" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB123" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AC120" s="4" t="inlineStr">
+      <c r="AC123" s="4" t="inlineStr">
         <is>
           <t>Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC120"/>
+  <autoFilter ref="A1:AC123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13212,7 +13509,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -13230,7 +13527,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13245,7 +13542,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -13278,7 +13575,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -13311,7 +13608,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -13344,7 +13641,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13362,7 +13659,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13410,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -13443,7 +13740,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -13476,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -13494,7 +13791,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13509,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -13542,7 +13839,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -13575,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13593,7 +13890,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13623,7 +13920,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -13632,7 +13929,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -13641,7 +13938,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -13659,7 +13956,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13674,7 +13971,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13689,13 +13986,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -13707,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -13722,16 +14019,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -13740,7 +14037,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -13758,7 +14055,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13773,7 +14070,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -13806,7 +14103,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -13824,7 +14121,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -13839,7 +14136,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -13857,7 +14154,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13872,7 +14169,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -13890,13 +14187,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.67</v>
+        <v>3.17</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -13923,7 +14220,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13938,7 +14235,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -13956,7 +14253,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -13971,7 +14268,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -14004,7 +14301,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -14022,13 +14319,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -14037,7 +14334,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 37 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="P3" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>2</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>1</v>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1826,8 +1826,8 @@
       <c r="R11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="9" t="n">
-        <v>1</v>
+      <c r="S11" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T11" s="9" t="n">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2724,17 +2724,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-29</v>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2768,11 +2768,11 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="9" t="n">
-        <v>0</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>7</v>
@@ -2780,8 +2780,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3901,8 +3901,8 @@
       <c r="S31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="9" t="n">
-        <v>0</v>
+      <c r="T31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U31" s="9" t="n">
         <v>0</v>
@@ -3968,17 +3968,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -3998,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4679,13 +4679,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4726,8 +4726,8 @@
       <c r="V39" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W39" s="9" t="n">
-        <v>3</v>
+      <c r="W39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>5</v>
@@ -4784,13 +4784,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4920,8 +4920,8 @@
       <c r="R41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="9" t="n">
-        <v>1</v>
+      <c r="S41" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T41" s="10" t="n">
         <v>1</v>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6327,13 +6327,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6529,13 +6529,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6779,11 +6779,11 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>3</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>6</v>
@@ -6876,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="9" t="n">
         <v>0</v>
@@ -6941,17 +6941,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-13</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -7452,17 +7452,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-19</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7969,13 +7969,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="10" t="n">
         <v>1</v>
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8074,13 +8074,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8118,8 +8118,8 @@
       <c r="U72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="9" t="n">
-        <v>1</v>
+      <c r="V72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8274,13 +8274,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8577,13 +8577,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8678,13 +8678,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8882,13 +8882,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>7</v>
@@ -9189,13 +9189,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" s="10" t="n">
         <v>1</v>
@@ -10576,7 +10576,7 @@
         <v>0</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10958,13 +10958,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>7</v>
@@ -11059,13 +11059,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11205,8 +11205,8 @@
       <c r="T102" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
+      <c r="U102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V102" s="10" t="n">
         <v>4</v>
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11574,13 +11574,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -12398,13 +12398,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12608,13 +12608,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>6</v>
@@ -13560,7 +13560,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13626,7 +13626,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13641,7 +13641,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -13725,7 +13725,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13740,7 +13740,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -13791,7 +13791,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13923,7 +13923,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -13971,7 +13971,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -13989,7 +13989,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -14187,7 +14187,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>3.17</v>
+        <v>3.33</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>

--- a/docs/d/74/inyear.xlsx
+++ b/docs/d/74/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1715,8 +1715,8 @@
       <c r="P10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="9" t="n">
-        <v>1</v>
+      <c r="Q10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -1896,17 +1896,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-36</v>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2143,8 +2143,8 @@
       <c r="T14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="9" t="n">
-        <v>0</v>
+      <c r="U14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>2</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2619,17 +2619,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M19" s="8" t="n">
@@ -2663,11 +2663,11 @@
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>0</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>7</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3184,8 +3184,8 @@
       <c r="U24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>3</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3451,13 +3451,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4705,8 +4705,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P39" s="9" t="n">
-        <v>3</v>
+      <c r="P39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5406,13 +5406,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>1</v>
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>6</v>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7046,13 +7046,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -8882,13 +8882,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>7</v>
@@ -8983,13 +8983,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9916,13 +9916,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>6</v>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10056,8 +10056,8 @@
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="9" t="n">
-        <v>1</v>
+      <c r="S91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T91" s="10" t="n">
         <v>1</v>
@@ -10231,13 +10231,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-22</v>
+        <v>-13</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>1</v>
@@ -11059,13 +11059,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -11164,13 +11164,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11197,10 +11197,10 @@
         <v>2</v>
       </c>
       <c r="R102" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S102" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T102" s="10" t="n">
         <v>1</v>
@@ -11212,7 +11212,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -11778,13 +11778,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -12398,13 +12398,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12503,17 +12503,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L115" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12538,8 +12538,8 @@
       <c r="R115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S115" s="9" t="n">
-        <v>1</v>
+      <c r="S115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T115" s="10" t="n">
         <v>1</v>
@@ -13020,13 +13020,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13575,7 +13575,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -13593,7 +13593,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13626,7 +13626,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13641,7 +13641,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -13659,7 +13659,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13791,13 +13791,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -14121,13 +14121,13 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -14253,7 +14253,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -14268,7 +14268,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
